--- a/backend/tests/reporting/output/test-case-catalog.xlsx
+++ b/backend/tests/reporting/output/test-case-catalog.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -507,12 +507,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>security/test_authentication.py</t>
+          <t>security/test_auth_token_matrix.py</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>test_no_auth_header_rejected_on_every_protected_endpoint</t>
+          <t>test_invalid_token_type_rejected_on_every_protected_endpoint</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Every protected endpoint rejects requests with no Authorization header</t>
+          <t>Every invalid-token type is rejected (401) on every protected endpoint</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sweep all get_current_user-gated routes, not just one sample.</t>
+          <t>11 token types x 7 endpoints = 77 real, independently meaningful checks -- confirms no single endpoint has a gap in its auth dependency wiring that would only show up for one specific kind of bad token.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
@@ -553,7 +553,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>test_garbage_bearer_token_rejected_on_every_protected_endpoint</t>
+          <t>test_no_auth_header_rejected_on_every_protected_endpoint</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -563,10 +563,14 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>A syntactically-invalid bearer token is rejected on every protected endpoint</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
+          <t>Every protected endpoint rejects requests with no Authorization header</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Sweep all get_current_user-gated routes, not just one sample.</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -590,7 +594,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>test_empty_bearer_token_rejected</t>
+          <t>test_garbage_bearer_token_rejected_on_every_protected_endpoint</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -600,14 +604,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>"Bearer " with no token value is rejected</t>
+          <t>A syntactically-invalid bearer token is rejected on every protected endpoint</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
@@ -627,7 +631,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>test_non_bearer_auth_scheme_rejected</t>
+          <t>test_empty_bearer_token_rejected</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -637,14 +641,10 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>A non-Bearer auth scheme (e.g. Basic) is rejected, not silently accepted</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>HTTPBearer(auto_error=False) should refuse to extract credentials from a differently-schemed header, leaving current_user falsy -&gt; 401.</t>
-        </is>
-      </c>
+          <t>"Bearer " with no token value is rejected</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>test_forged_alg_none_jwt_rejected</t>
+          <t>test_non_bearer_auth_scheme_rejected</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -678,18 +678,18 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>A self-signed / "alg: none" forged JWT asserting an arbitrary uid is rejected</t>
+          <t>A non-Bearer auth scheme (e.g. Basic) is rejected, not silently accepted</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Classic JWT-library vulnerability class: an attacker crafts a token with alg=none (or an unsigned/garbage signature) claiming any uid they like. Confirms the app relies on Firebase's real signature verification (auth.verify_id_token) rather than a naive decode.</t>
+          <t>HTTPBearer(auto_error=False) should refuse to extract credentials from a differently-schemed header, leaving current_user falsy -&gt; 401.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
@@ -709,7 +709,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>test_forged_hs256_jwt_with_guessed_secret_rejected</t>
+          <t>test_forged_alg_none_jwt_rejected</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>A JWT signed with the app's own SECRET_KEY (HS256) is still rejected</t>
+          <t>A self-signed / "alg: none" forged JWT asserting an arbitrary uid is rejected</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Firebase ID tokens are RS256, signed by Google -- the app's local SECRET_KEY (used elsewhere, e.g. for anything HS256-based) must NOT be a valid signing key for auth tokens. This guards against an algorithm-confusion attack where an attacker signs a token with a secret they can guess or find (e.g. a leaked .env).</t>
+          <t>Classic JWT-library vulnerability class: an attacker crafts a token with alg=none (or an unsigned/garbage signature) claiming any uid they like. Confirms the app relies on Firebase's real signature verification (auth.verify_id_token) rather than a naive decode.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>test_malformed_token_on_optional_auth_endpoint_degrades_to_anonymous</t>
+          <t>test_forged_hs256_jwt_with_guessed_secret_rejected</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -760,22 +760,18 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>A malformed token on an optional-auth endpoint never causes a 500</t>
+          <t>A JWT signed with the app's own SECRET_KEY (HS256) is still rejected</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>/scan/analyse uses get_current_user_optional, which must swallow verification errors and degrade to "anonymous", not propagate an exception.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>200 (treated as anonymous), never 401 or 500.</t>
-        </is>
-      </c>
+          <t>Firebase ID tokens are RS256, signed by Google -- the app's local SECRET_KEY (used elsewhere, e.g. for anything HS256-based) must NOT be a valid signing key for auth tokens. This guards against an algorithm-confusion attack where an attacker signs a token with a secret they can guess or find (e.g. a leaked .env).</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
@@ -795,25 +791,29 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>test_sql_injection_style_string_as_token_rejected</t>
+          <t>test_malformed_token_on_optional_auth_endpoint_degrades_to_anonymous</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Authentication / Injection</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>A SQLi-style payload used as the bearer token is rejected, not specially parsed</t>
+          <t>A malformed token on an optional-auth endpoint never causes a 500</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Confirm the token value is only ever passed to firebase_admin.auth.verify_id_token() (which will reject it as a malformed JWT) and never reaches a raw SQL string anywhere.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
+          <t>/scan/analyse uses get_current_user_optional, which must swallow verification errors and degrade to "anonymous", not propagate an exception.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>200 (treated as anonymous), never 401 or 500.</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -836,24 +836,28 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>test_oversized_token_does_not_crash_server</t>
+          <t>test_sql_injection_style_string_as_token_rejected</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Authentication / Input Validation</t>
+          <t>Authentication / Injection</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>An extremely long bearer token value is rejected cleanly, not a 500</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
+          <t>A SQLi-style payload used as the bearer token is rejected, not specially parsed</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Confirm the token value is only ever passed to firebase_admin.auth.verify_id_token() (which will reject it as a malformed JWT) and never reaches a raw SQL string anywhere.</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
@@ -868,29 +872,29 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>security/test_authorization_idor.py</t>
+          <t>security/test_authentication.py</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>test_user_cannot_list_another_users_history</t>
+          <t>test_oversized_token_does_not_crash_server</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Authorization / IDOR</t>
+          <t>Authentication / Input Validation</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>GET /history never returns another identity's scans</t>
+          <t>An extremely long bearer token value is rejected cleanly, not a 500</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
@@ -910,7 +914,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>test_user_cannot_fetch_another_users_history_item_by_id</t>
+          <t>test_user_cannot_list_another_users_history</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -920,14 +924,10 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>GET /history/{id} 404s for an id owned by a different identity</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Confirm this is a real 404 (ownership-checked), not a 403 that would leak "this id exists, just isn't yours" -- get_scan_or_404() filters by id AND user_id in a single query, so a non-owner sees the exact same response as a nonexistent id.</t>
-        </is>
-      </c>
+          <t>GET /history never returns another identity's scans</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>test_user_cannot_delete_another_users_history_item</t>
+          <t>test_user_cannot_fetch_another_users_history_item_by_id</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -961,10 +961,14 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>DELETE /history/{id} cannot delete another identity's item</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+          <t>GET /history/{id} 404s for an id owned by a different identity</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Confirm this is a real 404 (ownership-checked), not a 403 that would leak "this id exists, just isn't yours" -- get_scan_or_404() filters by id AND user_id in a single query, so a non-owner sees the exact same response as a nonexistent id.</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -988,7 +992,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>test_bulk_clear_history_only_affects_caller</t>
+          <t>test_user_cannot_delete_another_users_history_item</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -998,14 +1002,10 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>DELETE /history (bulk clear) is scoped to the caller only</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>clear_history() does `WHERE user_id == current_user["uid"]`. A missing WHERE clause here would wipe every user's history.</t>
-        </is>
-      </c>
+          <t>DELETE /history/{id} cannot delete another identity's item</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>test_users_do_not_see_each_others_profile_fields</t>
+          <t>test_bulk_clear_history_only_affects_caller</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1039,10 +1039,14 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Each identity's GET /users/me only ever reflects its own profile</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
+          <t>DELETE /history (bulk clear) is scoped to the caller only</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>clear_history() does `WHERE user_id == current_user["uid"]`. A missing WHERE clause here would wipe every user's history.</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -1066,7 +1070,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>test_deleting_own_profile_does_not_touch_other_users_data</t>
+          <t>test_users_do_not_see_each_others_profile_fields</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1076,14 +1080,10 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>DELETE /users/me only cascades within the caller's own data</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>delete_my_profile() cascades to ScanHistory filtered by the caller's own uid. Confirm a second identity's profile and history survive completely untouched.</t>
-        </is>
-      </c>
+          <t>Each identity's GET /users/me only ever reflects its own profile</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>test_history_id_enumeration_across_owners_always_404s_for_non_owner</t>
+          <t>test_deleting_own_profile_does_not_touch_other_users_data</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Sweeping a range of ids that DO exist (owned by someone else) never succeeds for a non-owner, even by chance</t>
+          <t>DELETE /users/me only cascades within the caller's own data</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Simulates an attacker enumerating small sequential integer ids (auto-increment primary key) hoping to hit someone else's record.</t>
+          <t>delete_my_profile() cascades to ScanHistory filtered by the caller's own uid. Confirm a second identity's profile and history survive completely untouched.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
@@ -1143,33 +1143,33 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>security/test_configuration_headers.py</t>
+          <t>security/test_authorization_idor.py</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>test_error_responses_are_valid_json_not_html</t>
+          <t>test_history_id_enumeration_across_owners_always_404s_for_non_owner</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Authorization / IDOR</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Every error path (404, 422, 429) returns application/json, never an HTML error page</t>
+          <t>Sweeping a range of ids that DO exist (owned by someone else) never succeeds for a non-owner, even by chance</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>A stray HTML error page is a common sign of an unhandled framework-level failure bypassing the app's own error handling.</t>
+          <t>Simulates an attacker enumerating small sequential integer ids (auto-increment primary key) hoping to hit someone else's record.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
@@ -1184,33 +1184,33 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>security/test_configuration_headers.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>test_cors_rejects_disallowed_origin</t>
+          <t>test_harmful_keyword_flagged_within_a_longer_ingredient_string</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Configuration / CORS</t>
+          <t>Business Logic</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>A preflight request from an origin not in ALLOWED_ORIGINS is rejected</t>
+          <t>A harmful keyword embedded inside a longer ingredient description is still caught</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Confirm CORSMiddleware is configured with an explicit allow-list (settings.ALLOWED_ORIGINS), not allow_origins=["*"].</t>
+          <t>Real ingredient labels rarely list bare keywords -- confirms substring matching works within realistic label text, e.g. "contains high fructose corn syrup (2%)".</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
@@ -1225,37 +1225,33 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>security/test_configuration_headers.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>test_cors_accepts_configured_origin</t>
+          <t>test_allergy_profile_flags_matching_ingredient_as_danger</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Configuration / CORS</t>
+          <t>Business Logic</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>A preflight request from an allow-listed origin succeeds and echoes that origin</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Also confirms the allow-list is origin-specific (not "*") even when allow_credentials=true -- required, since browsers reject wildcard-origin + credentials combinations anyway, but worth locking in.</t>
-        </is>
-      </c>
+          <t>A saved allergy correctly flags a matching ingredient as danger, overriding whatever its E-code/keyword status would otherwise be</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
@@ -1266,34 +1262,26 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>functional/test_system_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>test_global_exception_handler_hides_internals</t>
+          <t>test_allergy_check_is_case_insensitive</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Configuration / Error Handling</t>
+          <t>Business Logic</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Unhandled exceptions never leak internals to the client</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>app/main.py registers a catch-all exception handler (global_exception_handler). Force a downstream failure and confirm the client only ever sees the generic {"error": ..., "detail": ...} shape, never a Python traceback, file path, or exception message. NOTE: uses crash_test_client (raise_app_exceptions=False), confirmed by direct testing to be necessary here -- the default test clients' ASGITransport re-raises escaped exceptions into the test process instead of returning the response a real client gets. Verified against both a real uvicorn server and ASGITransport directly: production returns the sanitized body correctly; only the default test-client config would (incorrectly) look like the handler had failed.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>500 with the generic sanitized body.</t>
-        </is>
-      </c>
+          <t>Allergy matching works regardless of the case used for either the saved allergy or the ingredient name</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -1311,33 +1299,33 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>security/test_configuration_headers.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>test_openapi_schema_is_reachable</t>
+          <t>test_allergy_takes_priority_over_ecode_status</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Configuration / Information Disclosure</t>
+          <t>Business Logic</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>[INFORMATIONAL] /docs and /openapi.json are exposed with default FastAPI settings</t>
+          <t>A profile allergy match overrides an otherwise "safe" E-code classification</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Document the current state -- FastAPI's interactive docs are not disabled (no docs_url=None / openapi_url=None in main.py's FastAPI(...) constructor).</t>
+          <t>analyze_ingredients checks is_allergen BEFORE ecode_match in its final if/elif chain -- confirms that ordering holds even when the ingredient would otherwise resolve as a "safe" E-code.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
@@ -1352,29 +1340,29 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>security/test_configuration_headers.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>test_server_header_does_not_leak_detailed_version_info</t>
+          <t>test_empty_allergy_list_does_not_flag_anything</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Configuration / Information Disclosure</t>
+          <t>Business Logic</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>The Server response header (if present) doesn't reveal a specific framework/OS version</t>
+          <t>An empty allergies list behaves identically to no profile at all</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
@@ -1389,33 +1377,29 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>security/test_configuration_headers.py</t>
+          <t>unit/test_nova_classifier_matrix.py</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>test_no_hardening_security_headers_present</t>
+          <t>test_marker_matching_is_case_insensitive</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Configuration / Security Headers</t>
+          <t>Business Logic</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>[FINDING] No X-Content-Type-Options / X-Frame-Options / HSTS / CSP headers</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Confirms the current, undocumented state of the response headers on a plain JSON API response.</t>
-        </is>
-      </c>
+          <t>Marker matching works regardless of the ingredient's capitalization</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
@@ -1430,22 +1414,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>functional/test_history_functional.py</t>
+          <t>unit/test_nova_classifier_matrix.py</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>test_history_pagination_limit</t>
+          <t>test_marker_matched_within_a_longer_ingredient_string</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>limit truncates results to the requested page size</t>
+          <t>A marker embedded inside a longer, realistic ingredient description is still caught</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1467,33 +1451,37 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>functional/test_history_functional.py</t>
+          <t>unit/test_nova_classifier_matrix.py</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>test_history_pagination_offset</t>
+          <t>test_three_marker_threshold_boundary</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>offset skips the newest N items (list is newest-first)</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
+          <t>Exactly 3 distinct markers triggers class 4; 2 markers stays at class 3</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Verified the exact boundary directly: 2 markers -&gt; 3, 3 markers -&gt; 4.</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
@@ -1504,33 +1492,37 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>functional/test_history_functional.py</t>
+          <t>unit/test_nova_classifier_matrix.py</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>test_history_get_nonexistent_id_is_404</t>
+          <t>test_fifteen_item_length_threshold_boundary</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Fetching a history id that was never created returns 404</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
+          <t>An ingredient list of exactly 15 items stays under the ultra-processed length threshold; 16 items crosses it (regardless of marker count)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>`marker_count &gt;= 3 or len(ingredients) &gt; 15` -- verified the exact off-by-one boundary directly (15 items -&gt; False, still class 3 via the length&gt;8 rule; 16 items -&gt; True, class 4).</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
@@ -1541,25 +1533,29 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>functional/test_history_functional.py</t>
+          <t>unit/test_nova_classifier_matrix.py</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>test_clear_history_removes_everything</t>
+          <t>test_eight_item_length_threshold_boundary</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>DELETE /history (bulk clear) empties the list for that user</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
+          <t>An ingredient list of exactly 8 items (0 markers) stays at class 2; 9 items crosses to class 3</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>`marker_count &gt;= 1 or len(ingredients) &gt; 8` -- verified the exact boundary directly with 0 markers present.</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -1567,7 +1563,7 @@
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
@@ -1578,41 +1574,37 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>unit/test_nova_classifier_matrix.py</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>test_analyse_flags_known_ecode</t>
+          <t>test_three_item_length_threshold_boundary</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>A known E-number is classified using ecodes.json</t>
+          <t>An ingredient list of exactly 3 items (no markers, no oil/sugar) stays at class 1 (unprocessed); 4 items crosses to class 2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>E102 (Tartrazine) is seeded in app/data/ecodes.json as "danger".</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>200, ingredient status == "danger", reason mentions Tartrazine.</t>
-        </is>
-      </c>
+          <t>`len(ingredients) &gt; 3 or "oil" in all_text or "sugar" in all_text` -- verified the exact boundary directly.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
@@ -1623,37 +1615,33 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>unit/test_nova_classifier_matrix.py</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>test_analyse_fuzzy_matches_misspelled_full_name</t>
+          <t>test_oil_or_sugar_keyword_triggers_class_2_even_with_one_ingredient</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Fuzzy matching (rapidfuzz, threshold 80) catches near-misspellings</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>"curcumin" is E100's full_name. A close misspelling should still match via fuzz.WRatio &gt;= 80, not silently fall through to "safe".</t>
-        </is>
-      </c>
+          <t>"oil" or "sugar" anywhere in the ingredient text triggers at least class 2, even for a single-item list well under every length threshold</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
@@ -1664,37 +1652,29 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>unit/test_nova_classifier_matrix.py</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>test_analyse_harmful_keyword_without_ecode</t>
+          <t>test_single_plain_ingredient_is_class_1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Non-E-code harmful keyword list still flags ingredients</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>"palm oil" is in IngredientEngine.harmful_keywords, not ecodes.json.</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>status == "caution".</t>
-        </is>
-      </c>
+          <t>A single plain, unprocessed-sounding ingredient with no markers/oil/sugar is class 1</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
@@ -1709,22 +1689,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>unit/test_nova_classifier_matrix.py</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>test_analyse_is_case_insensitive</t>
+          <t>test_all_20_markers_present_together_is_class_4</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Ingredient matching is case-insensitive</t>
+          <t>An ingredient list containing every known marker classifies as class 4</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1746,33 +1726,33 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>test_analyse_duplicate_ingredients_all_returned</t>
+          <t>test_ecode_matched_by_code_name</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic / Data Integrity</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Duplicate ingredient entries are each analyzed and returned</t>
+          <t>Every E-code in ecodes.json is correctly classified by its own code name</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>The response must be positional/1:1 with the request, not deduplicated.</t>
+          <t>Exercises the direct substring-match step (step 1 in analyze_ingredients). A failure here for a single entry means either ecodes.json or the matching logic broke for that specific additive.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
@@ -1787,25 +1767,29 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>test_barcode_happy_path_with_full_product</t>
+          <t>test_ecode_matched_by_real_label_full_name</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic / Data Integrity</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>A full Open Food Facts product payload is analyzed end-to-end</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
+          <t>[FINDING - see module docstring] Every E-code should be correctly classified when entered in its real, natural product-label case</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Exercises the fuzzy-match step (step 2) using the exact capitalization a user would see on a real ingredient label -- not a pre-lowercased convenience string. 4 of 30 entries are confirmed broken by a case-sensitivity bug in the fuzzy matcher; see the module docstring for the full root-cause analysis with exact WRatio scores.</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
@@ -1824,27 +1808,27 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>test_barcode_missing_nova_group_defaults_to_4</t>
+          <t>test_ecode_actually_identified_by_real_label_full_name</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic / Data Integrity</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>A product missing nova_group defaults to the most conservative class (4)</t>
+          <t>[FINDING - see module docstring] The matcher should identify the CORRECT specific E-code entry, not just happen to land on the right status by coincidence</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>routers/scan.py does int(product.get("nova_group", 4)) -- confirm the fail-safe default is actually reached, not skipped.</t>
+          <t>Stricter than test_ecode_matched_by_real_label_full_name -- checks that the E-code's own full_name appears in the result reason (proof the right entry was actually selected), not just that the final status string happens to match. This catches one additional casualty (E412 "Guar Gum") that test_ecode_matched_by_real_label_full_name misses, because Guar Gum's broken match happens to fall through to a "safe" default that coincidentally equals its real status -- the identification is still broken, it's just invisible if you only check the final status.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
@@ -1865,37 +1849,29 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>functional/test_system_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>test_root_endpoint_shape</t>
+          <t>test_harmful_keyword_flagged_as_caution</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic / Data Integrity</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Root endpoint returns a stable status payload</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Confirm GET / never regresses to a 500 or a missing key.</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>200 with "message" and "status" keys.</t>
-        </is>
-      </c>
+          <t>Every non-E-code harmful keyword is flagged as caution</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
@@ -1910,37 +1886,33 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>functional/test_system_functional.py</t>
+          <t>unit/test_nova_classifier_matrix.py</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>test_health_endpoint_reports_all_subsystems</t>
+          <t>test_each_ultra_processed_marker_individually_triggers_class_3</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic / Data Integrity</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>/health reports db, redis, and environment</t>
+          <t>Every ultra_processed_markers entry, alone, triggers at least class 3</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Confirm the readiness probe contract used by Docker/CI healthchecks.</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>200 (even when a dependency is degraded -- see docker-compose.yml healthcheck, which polls this endpoint) with db/redis/environment keys.</t>
-        </is>
-      </c>
+          <t>A regression in this list (typo, removed entry) would silently under-classify processed foods. Confirms each of the 20 markers, in isolation (marker_count == 1, well under the 15-item length threshold), correctly triggers the "marker_count &gt;= 1" rule.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
@@ -1955,29 +1927,33 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>functional/test_system_functional.py</t>
+          <t>unit/test_nova_classifier_matrix.py</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>test_unknown_route_returns_404</t>
+          <t>test_empty_ingredient_list_does_not_crash</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic / Input Validation</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Unknown route returns 404, not a stack trace</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr"/>
+          <t>An empty ingredient list classifies as 1 (unprocessed) rather than crashing</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Relevant for a barcode product with no listed ingredients text.</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
@@ -1992,33 +1968,33 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>functional/test_system_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>test_wrong_method_returns_405</t>
+          <t>test_nova_deduction_formula_at_every_class</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Unsupported HTTP method on a known route returns 405</t>
+          <t>NOVA deduction follows (nova_class - 1) * 6.67, capped at 20, for every class 1-4</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>FastAPI's default routing must reject wrong verbs cleanly, not fall through to an unrelated handler.</t>
+          <t>This scoring formula has no dedicated boundary test in the original suite (only nova_class=1 and nova_class=4 were touched, and only combined with other deductions). Verified exact values by direct experimentation before writing these assertions.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
@@ -2033,27 +2009,27 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>functional/test_users_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>test_patch_partial_update_preserves_other_fields</t>
+          <t>test_additive_deduction_position_weighting</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>PATCH only updates the fields sent, leaving others untouched</t>
+          <t>A flagged ingredient's position in the list changes its score penalty weight</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>UserProfileUpdateRequest fields are all Optional; the router does `.model_dump(exclude_unset=True)`. Confirm a PATCH with only "goals" does not clobber a previously-set "allergies" list.</t>
+          <t>FSSAI-style labels list ingredients by descending weight, so the algorithm weights earlier positions more heavily (x3 for position 0, x2 for positions 1-2, x1 for positions 3-5, x0.5 for position 6+). Verified exact expected values by direct experimentation with the real calculate_hs_score before writing these assertions -- not derived purely by reading the source.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
@@ -2063,7 +2039,7 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
@@ -2074,29 +2050,33 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>functional/test_users_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>test_patch_empty_body_is_a_no_op</t>
+          <t>test_additive_deduction_caps_at_30</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>PATCH with an empty JSON body changes nothing and still returns 200</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
+          <t>additiveDeduction never exceeds 30, even when uncapped math would produce more</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Two "danger" (non-allergy) ingredients at positions 0 and 1 would sum to 10*3 + 10*2 = 50 uncapped; confirms the min(30.0, ...) cap.</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
@@ -2111,27 +2091,27 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>functional/test_users_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>test_get_profile_is_idempotent_auto_create</t>
+          <t>test_additive_deduction_sugar_keyword_bonus</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Calling GET /users/me twice does not error or duplicate the row</t>
+          <t>A "sugar"/"syrup"/"palm oil"/"fructose" name adds +4 to the base penalty</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>The auto-create-on-first-access path uses id as primary key, so a second GET should hit the SELECT branch, not attempt a second INSERT.</t>
+          <t>"caution" base penalty (5) + sugar bonus (4) = 9, x3 position multiplier at position 0 = 27. Verified exact value directly.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -2152,29 +2132,33 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>functional/test_users_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>test_unsupported_method_on_users_me</t>
+          <t>test_allergy_matched_ingredients_excluded_from_additive_deduction</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>PUT (unsupported verb) on /users/me returns 405</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr"/>
+          <t>An allergy-matched "danger" ingredient contributes to allergenDeduction, not additiveDeduction</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Confirms no double-counting -- the additive-penalty branch explicitly excludes items whose reason mentions "allergy".</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
@@ -2189,29 +2173,29 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>functional/test_users_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>test_display_name_round_trips</t>
+          <t>test_allergen_deduction_single_hit</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>display_name set via PATCH is returned verbatim by GET</t>
+          <t>A single allergy hit deducts exactly 40 points</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
@@ -2226,37 +2210,29 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>test_anonymous_scan_is_not_personalized_or_saved</t>
+          <t>test_allergen_deduction_caps_at_40_for_multiple_hits</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Functional API / Authorization</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>An unauthenticated scan never applies personalization</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>"peanut" only becomes "danger" against a profile that lists it as an allergy. With no auth token, current_user is None, so scan/analyse must use the empty default profile and must not attempt to save history (there is no user to attribute it to).</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>200, status != "danger" for a plain allergen name with no profile match.</t>
-        </is>
-      </c>
+          <t>Two allergy hits still deduct only 40 (capped), not 80</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
@@ -2271,37 +2247,29 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>functional/test_history_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>test_history_ordered_newest_first</t>
+          <t>test_allergen_deduction_zero_with_no_hits</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Functional API / Business Logic</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>[CONFIRMED BUG] History should be reliably ordered newest-first, even for scans made within the same second</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Simulates the common case of a user scanning several products back-to-back (well within one second in an automated test, but this is also realistic for a fast human scanner or a barcode-gun-style flow).</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>ids returned in descending (newest-first) order.</t>
-        </is>
-      </c>
+          <t>allergenDeduction is 0 when nothing matches a profile allergy</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
@@ -2316,41 +2284,37 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>functional/test_history_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>test_post_history_should_accept_offline_scan_sync</t>
+          <t>test_condition_deduction_per_condition</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Functional API / Business Logic</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>[KNOWN GAP] POST /history should let the mobile app push an offline-created scan</t>
+          <t>Each medical condition correctly deducts points when a matching keyword is present</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Document the desired contract for the mobile offline-sync flow.</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>201 with the created ScanHistoryResponse.</t>
-        </is>
-      </c>
+          <t>Verified each (condition, keyword) pair's exact deduction value directly against calculate_hs_score before writing assertions.</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
@@ -2361,33 +2325,29 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>test_authenticated_scan_applies_saved_allergy_profile</t>
+          <t>test_condition_deduction_no_match_is_zero</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Functional API / Business Logic</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>An authenticated scan is personalized against the user's saved allergies</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>End-to-end: create profile -&gt; set allergy -&gt; scan -&gt; "danger".</t>
-        </is>
-      </c>
+          <t>A condition with no matching keyword in the ingredient list deducts 0</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
@@ -2402,29 +2362,29 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>test_barcode_authenticated_scan_saved_to_history</t>
+          <t>test_condition_deduction_all_three_caps_at_20</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Functional API / Business Logic</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>An authenticated barcode scan is saved with the correct product metadata</t>
+          <t>All three conditions matching simultaneously caps at 20, not 15+12+10=37</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
@@ -2439,33 +2399,33 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>functional/test_users_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>test_patch_after_delete_returns_404_not_auto_create</t>
+          <t>test_unrecognized_condition_name_is_silently_ignored</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Functional API / Business Logic</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>PATCH does not auto-create a profile the way GET does</t>
+          <t>[FINDING] A condition name not in the hardcoded set (Diabetes/ Hypertension/High Cholesterol) is silently ignored, deducting nothing</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>update_my_profile() raises 404 if no row exists -- unlike get_my_profile(), it has no auto-create branch. Confirm that contract holds after a real delete.</t>
+          <t>schemas/user.py's "conditions" field is a free-text List[str] with no validation against a fixed enum -- a user (or a future frontend update) could save "Celiac Disease" or "Kidney Disease" and it would simply never affect scoring, with no error or warning anywhere.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
@@ -2480,33 +2440,33 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>test_analyse_unicode_ingredient_names</t>
+          <t>test_final_score_floors_at_zero_not_negative</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Functional API / Input Validation</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Non-ASCII ingredient names do not crash the pipeline</t>
+          <t>A worst-case combination (allergens + NOVA 4 + capped additives + all conditions) floors the score at exactly 0, never negative</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>rapidfuzz + string containment checks must handle unicode (e.g. accented characters, non-Latin scripts) without raising.</t>
+          <t>40 (allergen) + 20 (nova) + 30 (additive, capped) + 20 (condition) = 110 raw deduction against a 100-point scale. Confirmed directly this produces final_score == 0, not -10.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
@@ -2521,27 +2481,27 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>test_barcode_product_with_no_ingredients_text</t>
+          <t>test_all_safe_ingredients_score_100</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Functional API / Input Validation</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>A product with a missing/empty ingredients_text field doesn't crash</t>
+          <t>An all-safe ingredient list with NOVA class 1 scores a perfect 100</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>routers/scan.py does `.get("ingredients_text", "").split(",")` -- confirm the empty-string/None case degrades to an empty ingredient list, not an AttributeError on None.split(...).</t>
+          <t>Deliberately avoids "sugar"/"syrup"/"palm oil"/"fructose" in any ingredient name here -- see test_safe_status_ingredient_still_penalized_if_name_contains_sugar_keyword below for why those specific words are not a safe choice for this test.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -2562,33 +2522,33 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>test_analyse_large_ingredient_list_does_not_crash</t>
+          <t>test_safe_status_ingredient_still_penalized_if_name_contains_sugar_keyword</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Functional API / Performance</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>A large (200-item) ingredient list completes without error</t>
+          <t>[FINDING] An ingredient classified "safe" by analyze_ingredients can still be scored down by calculate_hs_score if its name contains "sugar", "syrup", "palm oil", or "fructose"</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Guard against O(n^2) fuzzy-matching blowups or timeouts on realistic worst-case label lengths.</t>
+          <t>calculate_hs_score's additive-penalty loop has a SEPARATE, independent keyword check -- `if any(x in name_lower for x in ["sugar", "syrup", "palm oil", "fructose"])` -- that applies regardless of the ingredient's status field. A plain ingredient named "sugar" is classified "safe" by analyze_ingredients (it's not in ecodes.json or harmful_keywords), but calculate_hs_score still deducts points for it via this separate name-based check. Confirmed directly: ["water","salt","sugar"] at nova_class=1 scores 92, not 100, solely because of "sugar" appearing third in the list.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
@@ -2603,33 +2563,29 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>security/test_input_validation_injection.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>test_injection_payload_in_ingredient_name_does_not_crash</t>
+          <t>test_empty_ingredient_list_scores_100</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Injection</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Injection-style strings as an ingredient name are handled as inert data</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Confirm the request completes normally (200) and the payload is returned back as a literal, unexecuted string -- it never reaches a shell, template engine, or raw SQL string anywhere in the pipeline.</t>
-        </is>
-      </c>
+          <t>An empty ingredient list (e.g. a barcode product with no listed ingredients) still produces a valid, non-crashing score</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
@@ -2644,29 +2600,33 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>security/test_input_validation_injection.py</t>
+          <t>security/test_configuration_headers.py</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>test_injection_payload_in_allergy_list_does_not_crash</t>
+          <t>test_error_responses_are_valid_json_not_html</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Injection</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Injection-style strings in a PATCH'd allergies list are stored as inert data</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
+          <t>Every error path (404, 422, 429) returns application/json, never an HTML error page</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>A stray HTML error page is a common sign of an unhandled framework-level failure bypassing the app's own error handling.</t>
+        </is>
+      </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
@@ -2681,25 +2641,29 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>security/test_input_validation_injection.py</t>
+          <t>security/test_configuration_headers.py</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>test_sql_injection_in_barcode_field_does_not_crash</t>
+          <t>test_cors_rejects_disallowed_origin</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Injection</t>
+          <t>Configuration / CORS</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>A SQLi-style barcode value is handled as an opaque string, not executed</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
+          <t>A preflight request from an origin not in ALLOWED_ORIGINS is rejected</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Confirm CORSMiddleware is configured with an explicit allow-list (settings.ALLOWED_ORIGINS), not allow_origins=["*"].</t>
+        </is>
+      </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -2718,33 +2682,33 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>security/test_input_validation_injection.py</t>
+          <t>security/test_configuration_headers.py</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>test_display_name_xss_payload_returned_as_literal_json_string</t>
+          <t>test_cors_accepts_configured_origin</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Injection</t>
+          <t>Configuration / CORS</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>An XSS-style display_name is stored/returned as an inert JSON string value</t>
+          <t>A preflight request from an allow-listed origin succeeds and echoes that origin</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>This is a JSON API, not server-rendered HTML, so there is no HTML-escaping expectation here -- the responsibility to escape on render belongs to the frontend. This test only confirms the backend doesn't do anything unsafe with it server-side (e.g. no crash, no reflected-unescaped-into-HTML anywhere in this service).</t>
+          <t>Also confirms the allow-list is origin-specific (not "*") even when allow_credentials=true -- required, since browsers reject wildcard-origin + credentials combinations anyway, but worth locking in.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
@@ -2759,33 +2723,37 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>security/test_input_validation_injection.py</t>
+          <t>functional/test_system_functional.py</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>test_barcode_value_reaches_outbound_url_unsanitized</t>
+          <t>test_global_exception_handler_hides_internals</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Injection / Configuration</t>
+          <t>Configuration / Error Handling</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>[FINDING] The barcode field has no format/character validation before being concatenated into the outbound Open Food Facts request URL</t>
+          <t>Unhandled exceptions never leak internals to the client</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>schemas/scan.py declares BarcodeRequest.barcode as a bare str (no regex/length constraint), and services/off_client.py builds the request URL via an f-string: f"{base_url}/{barcode}.json" -- not urljoin, not URL-encoded, not validated as numeric.</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr"/>
+          <t>app/main.py registers a catch-all exception handler (global_exception_handler). Force a downstream failure and confirm the client only ever sees the generic {"error": ..., "detail": ...} shape, never a Python traceback, file path, or exception message. NOTE: uses crash_test_client (raise_app_exceptions=False), confirmed by direct testing to be necessary here -- the default test clients' ASGITransport re-raises escaped exceptions into the test process instead of returning the response a real client gets. Verified against both a real uvicorn server and ASGITransport directly: production returns the sanitized body correctly; only the default test-client config would (incorrectly) look like the handler had failed.</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>500 with the generic sanitized body.</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
@@ -2800,33 +2768,37 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>functional/test_history_functional.py</t>
+          <t>security/test_configuration_headers.py</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>test_history_limit_out_of_bounds_is_422</t>
+          <t>test_openapi_schema_is_reachable</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Configuration / Information Disclosure</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>limit outside [1, 100] (Query(20, ge=1, le=100)) is rejected</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
+          <t>[INFORMATIONAL] /docs and /openapi.json are exposed with default FastAPI settings</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Document the current state -- FastAPI's interactive docs are not disabled (no docs_url=None / openapi_url=None in main.py's FastAPI(...) constructor).</t>
+        </is>
+      </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
@@ -2837,29 +2809,29 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>functional/test_history_functional.py</t>
+          <t>security/test_configuration_headers.py</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>test_history_offset_negative_is_422</t>
+          <t>test_server_header_does_not_leak_detailed_version_info</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Configuration / Information Disclosure</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>A negative offset (Query(0, ge=0)) is rejected</t>
+          <t>The Server response header (if present) doesn't reveal a specific framework/OS version</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H60" s="2" t="n">
@@ -2874,25 +2846,29 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>functional/test_history_functional.py</t>
+          <t>security/test_configuration_headers.py</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>test_history_get_non_numeric_id_is_422</t>
+          <t>test_no_hardening_security_headers_present</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Configuration / Security Headers</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>A non-integer path id is rejected by FastAPI's path converter</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
+          <t>[FINDING] No X-Content-Type-Options / X-Frame-Options / HSTS / CSP headers</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Confirms the current, undocumented state of the response headers on a plain JSON API response.</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -2911,25 +2887,29 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>test_analyse_missing_ingredients_field_is_422</t>
+          <t>test_ecodes_json_has_no_duplicate_codes</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Data Integrity</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Missing required field returns a clean 422, not a 500</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+          <t>ecodes.json has no duplicate "name" entries</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>A duplicate would mean whichever entry appears first in the list silently shadows the other for the direct-match step -- the second entry would be permanently unreachable dead data.</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -2948,22 +2928,22 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>unit/test_ingredient_engine_matrix.py</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>test_analyse_wrong_type_for_ingredients_is_422</t>
+          <t>test_ecodes_json_every_entry_has_required_fields</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Data Integrity</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Non-list "ingredients" value is rejected by Pydantic, not cast</t>
+          <t>Every ecodes.json entry has all required fields with valid values</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -2985,29 +2965,25 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>functional/test_history_functional.py</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>test_analyse_non_string_items_in_list_is_422</t>
+          <t>test_history_pagination_limit</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>A list containing non-string items (numbers, objects, null) is rejected</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Confirms Pydantic's List[str] coercion doesn't silently stringify or crash on int/dict/None entries.</t>
-        </is>
-      </c>
+          <t>limit truncates results to the requested page size</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -3026,22 +3002,22 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>functional/test_scan_functional.py</t>
+          <t>functional/test_history_functional.py</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>test_barcode_missing_field_is_422</t>
+          <t>test_history_pagination_offset</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Missing "barcode" field returns 422</t>
+          <t>offset skips the newest N items (list is newest-first)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -3063,29 +3039,29 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>functional/test_users_functional.py</t>
+          <t>functional/test_history_functional.py</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>test_patch_invalid_type_for_allergies_is_422</t>
+          <t>test_history_get_nonexistent_id_is_404</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>PATCH rejects a non-list value for a list field</t>
+          <t>Fetching a history id that was never created returns 404</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H66" s="2" t="n">
@@ -3100,29 +3076,25 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>security/test_input_validation_injection.py</t>
+          <t>functional/test_history_functional.py</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>test_nested_object_where_string_expected_is_422</t>
+          <t>test_clear_history_removes_everything</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>A JSON object/array injected where a string is expected is rejected by Pydantic</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>NoSQL-injection-style payloads (e.g. {"$ne": null}) must be caught by strict typing, never coerced or passed through.</t>
-        </is>
-      </c>
+          <t>DELETE /history (bulk clear) empties the list for that user</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -3141,25 +3113,29 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>security/test_input_validation_injection.py</t>
+          <t>functional/test_http_method_matrix.py</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>test_top_level_array_instead_of_object_is_422</t>
+          <t>test_unimplemented_method_returns_405</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>A top-level JSON array where an object is expected is rejected, not a 500</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr"/>
+          <t>Every unimplemented (route, method) combination returns 405, not 404/500/2xx</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Uses an authenticated client throughout (auth_client) so a 405 is never confused with a 401 -- if a route required auth and returned 401 instead of 405 for a wrong-but-otherwise-valid method, that would mean method routing happens after auth instead of before, which is the wrong order for a clean API contract.</t>
+        </is>
+      </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -3167,7 +3143,7 @@
         </is>
       </c>
       <c r="H68" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
@@ -3178,26 +3154,34 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>security/test_input_validation_injection.py</t>
+          <t>functional/test_scan_functional.py</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>test_malformed_json_body_is_422</t>
+          <t>test_analyse_flags_known_ecode</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Syntactically invalid JSON returns 422, not a 500</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr"/>
+          <t>A known E-number is classified using ecodes.json</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>E102 (Tartrazine) is seeded in app/data/ecodes.json as "danger".</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>200, ingredient status == "danger", reason mentions Tartrazine.</t>
+        </is>
+      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -3215,33 +3199,33 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>security/test_input_validation_injection.py</t>
+          <t>functional/test_scan_functional.py</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>test_extremely_long_single_ingredient_does_not_crash</t>
+          <t>test_analyse_fuzzy_matches_misspelled_full_name</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Input Validation / Denial of Service</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>A single 100,000-character ingredient string does not crash or hang</t>
+          <t>Fuzzy matching (rapidfuzz, threshold 80) catches near-misspellings</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>There is no max_length constraint on ingredient strings today. Confirm the fuzzy-matching pass at least degrades gracefully rather than raising, since this is a realistic abuse vector (no size cap on the request body either).</t>
+          <t>"curcumin" is E100's full_name. A close misspelling should still match via fuzz.WRatio &gt;= 80, not silently fall through to "safe".</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
@@ -3256,33 +3240,37 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>security/test_rate_limiting.py</t>
+          <t>functional/test_scan_functional.py</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>test_rate_limit_does_not_block_a_completely_unrelated_request_body</t>
+          <t>test_analyse_harmful_keyword_without_ecode</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>The limiter keys on client identity + route, not on request content</t>
+          <t>Non-E-code harmful keyword list still flags ingredients</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Confirm varying the ingredients payload doesn't let a client dodge the limit (i.e. the limiter isn't accidentally keyed on a hash of the body, which would make it trivially bypassable).</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
+          <t>"palm oil" is in IngredientEngine.harmful_keywords, not ecodes.json.</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>status == "caution".</t>
+        </is>
+      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H71" s="2" t="n">
@@ -3297,33 +3285,29 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>security/test_rate_limiting.py</t>
+          <t>functional/test_scan_functional.py</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>test_scan_analyse_and_scan_barcode_have_independent_buckets</t>
+          <t>test_analyse_is_case_insensitive</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Exhausting /scan/analyse's quota does not affect /scan/barcode</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Each @limiter.limit(...) decorator is evaluated per-route. Confirm that's actually true end-to-end, not just true by code inspection -- a shared global bucket would be a functional regression.</t>
-        </is>
-      </c>
+          <t>Ingredient matching is case-insensitive</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H72" s="2" t="n">
@@ -3338,27 +3322,27 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>security/test_rate_limiting.py</t>
+          <t>functional/test_scan_functional.py</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>test_authenticated_endpoints_have_no_rate_limit_configured</t>
+          <t>test_analyse_duplicate_ingredients_all_returned</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting / Configuration</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>[FINDING] /users/me and /history have no @limiter.limit(...) at all</t>
+          <t>Duplicate ingredient entries are each analyzed and returned</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>main.py only wires the limiter's exception handler and state; routers/user.py and routers/history.py never import or apply @limiter. This test demonstrates the current (unlimited) behavior explicitly rather than leaving it undocumented.</t>
+          <t>The response must be positional/1:1 with the request, not deduplicated.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -3379,22 +3363,22 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>security/test_rate_limiting.py</t>
+          <t>functional/test_scan_functional.py</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>test_scan_analyse_allows_exactly_30_requests_per_minute</t>
+          <t>test_barcode_happy_path_with_full_product</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting / DAST</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>POST /scan/analyse permits exactly the documented 30 requests, then blocks</t>
+          <t>A full Open Food Facts product payload is analyzed end-to-end</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -3416,29 +3400,33 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>security/test_rate_limiting.py</t>
+          <t>functional/test_scan_functional.py</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>test_scan_analyse_31st_request_in_window_is_429</t>
+          <t>test_barcode_missing_nova_group_defaults_to_4</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting / DAST</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>The 31st request within the same minute is rejected with 429</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr"/>
+          <t>A product missing nova_group defaults to the most conservative class (4)</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>routers/scan.py does int(product.get("nova_group", 4)) -- confirm the fail-safe default is actually reached, not skipped.</t>
+        </is>
+      </c>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H75" s="2" t="n">
@@ -3453,27 +3441,39 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>test_history.py</t>
+          <t>functional/test_system_functional.py</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>test_list_history_empty</t>
+          <t>test_root_endpoint_shape</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>list history empty</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
+          <t>Root endpoint returns a stable status payload</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Confirm GET / never regresses to a 500 or a missing key.</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>200 with "message" and "status" keys.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="n">
         <v>1</v>
       </c>
@@ -3486,27 +3486,39 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>test_history.py</t>
+          <t>functional/test_system_functional.py</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>test_create_history_via_scan_and_list</t>
+          <t>test_health_endpoint_reports_all_subsystems</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>create history via scan and list</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr"/>
+          <t>/health reports db, redis, and environment</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Confirm the readiness probe contract used by Docker/CI healthchecks.</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>200 (even when a dependency is degraded -- see docker-compose.yml healthcheck, which polls this endpoint) with db/redis/environment keys.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="n">
         <v>1</v>
       </c>
@@ -3519,27 +3531,31 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>test_history.py</t>
+          <t>functional/test_system_functional.py</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>test_history_ownership</t>
+          <t>test_unknown_route_returns_404</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>history ownership</t>
+          <t>Unknown route returns 404, not a stack trace</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="n">
         <v>1</v>
       </c>
@@ -3552,29 +3568,37 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>test_ingredient_engine.py</t>
+          <t>functional/test_system_functional.py</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>test_ingredient_engine_analyze</t>
+          <t>test_wrong_method_returns_405</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>ingredient engine analyze</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr"/>
+          <t>Unsupported HTTP method on a known route returns 405</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>FastAPI's default routing must reject wrong verbs cleanly, not fall through to an unrelated handler.</t>
+        </is>
+      </c>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
@@ -3585,27 +3609,35 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>test_ingredient_engine.py</t>
+          <t>functional/test_users_functional.py</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>test_ingredient_engine_score</t>
+          <t>test_patch_partial_update_preserves_other_fields</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>ingredient engine score</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
+          <t>PATCH only updates the fields sent, leaving others untouched</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>UserProfileUpdateRequest fields are all Optional; the router does `.model_dump(exclude_unset=True)`. Confirm a PATCH with only "goals" does not clobber a previously-set "allergies" list.</t>
+        </is>
+      </c>
       <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="n">
         <v>1</v>
       </c>
@@ -3618,27 +3650,31 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>test_nova_classifier.py</t>
+          <t>functional/test_users_functional.py</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>test_nova_classify</t>
+          <t>test_patch_empty_body_is_a_no_op</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>nova classify</t>
+          <t>PATCH with an empty JSON body changes nothing and still returns 200</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="n">
         <v>1</v>
       </c>
@@ -3651,27 +3687,35 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>test_scan.py</t>
+          <t>functional/test_users_functional.py</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>test_analyse_ingredients_happy_path</t>
+          <t>test_get_profile_is_idempotent_auto_create</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>analyse ingredients happy path</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
+          <t>Calling GET /users/me twice does not error or duplicate the row</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>The auto-create-on-first-access path uses id as primary key, so a second GET should hit the SELECT branch, not attempt a second INSERT.</t>
+        </is>
+      </c>
       <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="n">
         <v>1</v>
       </c>
@@ -3684,27 +3728,31 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>test_scan.py</t>
+          <t>functional/test_users_functional.py</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>test_analyse_ingredients_empty</t>
+          <t>test_unsupported_method_on_users_me</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>analyse ingredients empty</t>
+          <t>PUT (unsupported verb) on /users/me returns 405</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="n">
         <v>1</v>
       </c>
@@ -3717,27 +3765,31 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>test_scan.py</t>
+          <t>functional/test_users_functional.py</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>test_analyse_barcode_not_found</t>
+          <t>test_display_name_round_trips</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>analyse barcode not found</t>
+          <t>display_name set via PATCH is returned verbatim by GET</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="n">
         <v>1</v>
       </c>
@@ -3750,27 +3802,39 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>test_users.py</t>
+          <t>functional/test_scan_functional.py</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>test_get_profile_unauthorized</t>
+          <t>test_anonymous_scan_is_not_personalized_or_saved</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Functional API / Authorization</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>get profile unauthorized</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr"/>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
+          <t>An unauthenticated scan never applies personalization</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>"peanut" only becomes "danger" against a profile that lists it as an allergy. With no auth token, current_user is None, so scan/analyse must use the empty default profile and must not attempt to save history (there is no user to attribute it to).</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>200, status != "danger" for a plain allergen name with no profile match.</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="n">
         <v>1</v>
       </c>
@@ -3783,27 +3847,39 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>test_users.py</t>
+          <t>functional/test_history_functional.py</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>test_get_profile_authorized</t>
+          <t>test_history_ordered_newest_first</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Functional API / Business Logic</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>get profile authorized</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
+          <t>[CONFIRMED BUG] History should be reliably ordered newest-first, even for scans made within the same second</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Simulates the common case of a user scanning several products back-to-back (well within one second in an automated test, but this is also realistic for a fast human scanner or a barcode-gun-style flow).</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>ids returned in descending (newest-first) order.</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="n">
         <v>1</v>
       </c>
@@ -3816,27 +3892,39 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>test_users.py</t>
+          <t>functional/test_history_functional.py</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>test_patch_profile</t>
+          <t>test_post_history_should_accept_offline_scan_sync</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Functional API / Business Logic</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>patch profile</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr"/>
-      <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
+          <t>[KNOWN GAP] POST /history should let the mobile app push an offline-created scan</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Document the desired contract for the mobile offline-sync flow.</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>201 with the created ScanHistoryResponse.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="n">
         <v>1</v>
       </c>
@@ -3849,31 +3937,1519 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>functional/test_scan_functional.py</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>test_authenticated_scan_applies_saved_allergy_profile</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional API / Business Logic</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>An authenticated scan is personalized against the user's saved allergies</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>End-to-end: create profile -&gt; set allergy -&gt; scan -&gt; "danger".</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>functional/test_scan_functional.py</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>test_barcode_authenticated_scan_saved_to_history</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional API / Business Logic</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>An authenticated barcode scan is saved with the correct product metadata</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>functional/test_users_functional.py</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>test_patch_after_delete_returns_404_not_auto_create</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional API / Business Logic</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>PATCH does not auto-create a profile the way GET does</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>update_my_profile() raises 404 if no row exists -- unlike get_my_profile(), it has no auto-create branch. Confirm that contract holds after a real delete.</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>functional/test_scan_functional.py</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>test_analyse_unicode_ingredient_names</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional API / Input Validation</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Non-ASCII ingredient names do not crash the pipeline</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>rapidfuzz + string containment checks must handle unicode (e.g. accented characters, non-Latin scripts) without raising.</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>functional/test_scan_functional.py</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>test_barcode_product_with_no_ingredients_text</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional API / Input Validation</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>A product with a missing/empty ingredients_text field doesn't crash</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>routers/scan.py does `.get("ingredients_text", "").split(",")` -- confirm the empty-string/None case degrades to an empty ingredient list, not an AttributeError on None.split(...).</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>functional/test_scan_functional.py</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>test_analyse_large_ingredient_list_does_not_crash</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional API / Performance</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>A large (200-item) ingredient list completes without error</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Guard against O(n^2) fuzzy-matching blowups or timeouts on realistic worst-case label lengths.</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>security/test_input_validation_injection.py</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>test_injection_payload_in_ingredient_name_does_not_crash</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Injection</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Injection-style strings as an ingredient name are handled as inert data</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Confirm the request completes normally (200) and the payload is returned back as a literal, unexecuted string -- it never reaches a shell, template engine, or raw SQL string anywhere in the pipeline.</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>security/test_input_validation_injection.py</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>test_injection_payload_in_allergy_list_does_not_crash</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Injection</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Injection-style strings in a PATCH'd allergies list are stored as inert data</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>security/test_input_validation_injection.py</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>test_sql_injection_in_barcode_field_does_not_crash</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Injection</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>A SQLi-style barcode value is handled as an opaque string, not executed</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>security/test_input_validation_injection.py</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>test_display_name_xss_payload_returned_as_literal_json_string</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Injection</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>An XSS-style display_name is stored/returned as an inert JSON string value</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>This is a JSON API, not server-rendered HTML, so there is no HTML-escaping expectation here -- the responsibility to escape on render belongs to the frontend. This test only confirms the backend doesn't do anything unsafe with it server-side (e.g. no crash, no reflected-unescaped-into-HTML anywhere in this service).</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>security/test_input_validation_injection.py</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>test_barcode_value_reaches_outbound_url_unsanitized</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Injection / Configuration</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>[FINDING] The barcode field has no format/character validation before being concatenated into the outbound Open Food Facts request URL</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>schemas/scan.py declares BarcodeRequest.barcode as a bare str (no regex/length constraint), and services/off_client.py builds the request URL via an f-string: f"{base_url}/{barcode}.json" -- not urljoin, not URL-encoded, not validated as numeric.</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>functional/test_history_functional.py</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>test_history_limit_out_of_bounds_is_422</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>limit outside [1, 100] (Query(20, ge=1, le=100)) is rejected</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>functional/test_history_functional.py</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>test_history_offset_negative_is_422</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>A negative offset (Query(0, ge=0)) is rejected</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>functional/test_history_functional.py</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>test_history_get_non_numeric_id_is_422</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>A non-integer path id is rejected by FastAPI's path converter</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>functional/test_scan_functional.py</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>test_analyse_missing_ingredients_field_is_422</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Missing required field returns a clean 422, not a 500</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>functional/test_scan_functional.py</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>test_analyse_wrong_type_for_ingredients_is_422</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Non-list "ingredients" value is rejected by Pydantic, not cast</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>functional/test_scan_functional.py</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>test_analyse_non_string_items_in_list_is_422</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>A list containing non-string items (numbers, objects, null) is rejected</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Confirms Pydantic's List[str] coercion doesn't silently stringify or crash on int/dict/None entries.</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>functional/test_scan_functional.py</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>test_barcode_missing_field_is_422</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Missing "barcode" field returns 422</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>functional/test_users_functional.py</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>test_patch_invalid_type_for_allergies_is_422</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>PATCH rejects a non-list value for a list field</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>security/test_input_validation_injection.py</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>test_nested_object_where_string_expected_is_422</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>A JSON object/array injected where a string is expected is rejected by Pydantic</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>NoSQL-injection-style payloads (e.g. {"$ne": null}) must be caught by strict typing, never coerced or passed through.</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>security/test_input_validation_injection.py</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>test_top_level_array_instead_of_object_is_422</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>A top-level JSON array where an object is expected is rejected, not a 500</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>security/test_input_validation_injection.py</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>test_malformed_json_body_is_422</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Syntactically invalid JSON returns 422, not a 500</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>security/test_input_validation_injection.py</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>test_extremely_long_single_ingredient_does_not_crash</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation / Denial of Service</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>A single 100,000-character ingredient string does not crash or hang</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>There is no max_length constraint on ingredient strings today. Confirm the fuzzy-matching pass at least degrades gracefully rather than raising, since this is a realistic abuse vector (no size cap on the request body either).</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>security/test_rate_limiting.py</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>test_rate_limit_does_not_block_a_completely_unrelated_request_body</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Rate Limiting</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>The limiter keys on client identity + route, not on request content</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Confirm varying the ingredients payload doesn't let a client dodge the limit (i.e. the limiter isn't accidentally keyed on a hash of the body, which would make it trivially bypassable).</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>security/test_rate_limiting.py</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>test_scan_analyse_and_scan_barcode_have_independent_buckets</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Rate Limiting</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Exhausting /scan/analyse's quota does not affect /scan/barcode</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Each @limiter.limit(...) decorator is evaluated per-route. Confirm that's actually true end-to-end, not just true by code inspection -- a shared global bucket would be a functional regression.</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>security/test_rate_limiting.py</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>test_authenticated_endpoints_have_no_rate_limit_configured</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Rate Limiting / Configuration</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>[FINDING] /users/me and /history have no @limiter.limit(...) at all</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>main.py only wires the limiter's exception handler and state; routers/user.py and routers/history.py never import or apply @limiter. This test demonstrates the current (unlimited) behavior explicitly rather than leaving it undocumented.</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>security/test_rate_limiting.py</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>test_scan_analyse_allows_exactly_30_requests_per_minute</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Rate Limiting / DAST</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>POST /scan/analyse permits exactly the documented 30 requests, then blocks</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>security/test_rate_limiting.py</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>test_scan_analyse_31st_request_in_window_is_429</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Rate Limiting / DAST</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>The 31st request within the same minute is rejected with 429</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>test_history.py</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>test_list_history_empty</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>list history empty</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>test_history.py</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>test_create_history_via_scan_and_list</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>create history via scan and list</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>test_history.py</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>test_history_ownership</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>history ownership</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>test_ingredient_engine.py</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>test_ingredient_engine_analyze</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>ingredient engine analyze</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>test_ingredient_engine.py</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>test_ingredient_engine_score</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>ingredient engine score</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>test_nova_classifier.py</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>test_nova_classify</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>nova classify</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>test_scan.py</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>test_analyse_ingredients_happy_path</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>analyse ingredients happy path</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>test_scan.py</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>test_analyse_ingredients_empty</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>analyse ingredients empty</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>test_scan.py</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>test_analyse_barcode_not_found</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>analyse barcode not found</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
           <t>test_users.py</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>test_get_profile_unauthorized</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>get profile unauthorized</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>test_users.py</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>test_get_profile_authorized</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>get profile authorized</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>test_users.py</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>test_patch_profile</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>patch profile</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>test_users.py</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>test_delete_profile</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>delete profile</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I88" s="3" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" s="3" t="inlineStr">
         <is>
           <t>not run</t>
         </is>
@@ -3890,7 +5466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3916,7 +5492,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3">
@@ -3926,7 +5502,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>116</v>
+        <v>409</v>
       </c>
     </row>
     <row r="4">
@@ -3936,7 +5512,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -3954,107 +5530,107 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Functional API</t>
+          <t>Business Logic / Scoring Algorithm</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Functional API</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Business Logic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Input Validation</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Authorization / IDOR</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Functional API / Business Logic</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Injection</t>
+          <t>Authorization / IDOR</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Functional API / Input Validation</t>
+          <t>Functional API / Business Logic</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Configuration / CORS</t>
+          <t>Business Logic / Data Integrity</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Configuration / Information Disclosure</t>
+          <t>Injection</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rate Limiting / DAST</t>
+          <t>Functional API / Input Validation</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -4064,7 +5640,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rate Limiting</t>
+          <t>Configuration / CORS</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -4074,47 +5650,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Functional API / Performance</t>
+          <t>Configuration / Information Disclosure</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Functional API / Authorization</t>
+          <t>Rate Limiting / DAST</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Configuration / Error Handling</t>
+          <t>Rate Limiting</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Authentication / Injection</t>
+          <t>Data Integrity</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Authentication / Input Validation</t>
+          <t>Functional API / Performance</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -4124,7 +5700,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Configuration / Security Headers</t>
+          <t>Functional API / Authorization</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -4134,7 +5710,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Configuration / Error Handling</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -4144,7 +5720,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Injection / Configuration</t>
+          <t>Authentication / Injection</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -4154,7 +5730,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Input Validation / Denial of Service</t>
+          <t>Authentication / Input Validation</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -4164,10 +5740,60 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Configuration / Security Headers</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Injection / Configuration</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Input Validation / Denial of Service</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Rate Limiting / Configuration</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Business Logic / Input Validation</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
         <v>1</v>
       </c>
     </row>
